--- a/Modbus_Map.xlsx
+++ b/Modbus_Map.xlsx
@@ -5,43 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\21023\PycharmProjects\260503modbus-python版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\21023\Documents\Code Projects\260503modbus-python版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73EF9D8-7056-4B39-A51D-B747695711C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFC5E9D-506D-446D-A3DF-C19314A2681A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="1716" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modbus_Map" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
-  <si>
-    <t>当前系统时间[0]</t>
-  </si>
-  <si>
-    <t>当前系统时间[1]</t>
-  </si>
-  <si>
-    <t>当前系统时间[2]</t>
-  </si>
-  <si>
-    <t>当前系统时间[3]</t>
-  </si>
-  <si>
-    <t>当前系统时间[4]</t>
-  </si>
-  <si>
-    <t>当前系统时间[5]</t>
-  </si>
-  <si>
-    <t>实验</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Bool</t>
   </si>
@@ -57,31 +36,28 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>当前系统时间</t>
-  </si>
-  <si>
-    <t>Array[0..9] of Int</t>
+    <t>准备就绪信号</t>
+  </si>
+  <si>
+    <t>当前楼层</t>
   </si>
   <si>
     <t>Int</t>
   </si>
   <si>
-    <t>当前系统时间[6]</t>
-  </si>
-  <si>
-    <t>当前系统时间[7]</t>
-  </si>
-  <si>
-    <t>当前系统时间[8]</t>
-  </si>
-  <si>
-    <t>当前系统时间[9]</t>
+    <t>Real</t>
+  </si>
+  <si>
+    <t>当前载重量</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -125,9 +101,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -432,160 +411,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1">
         <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="C3" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2">
         <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>